--- a/public/templates/office/EMP_DEG_070_코드정의서.xlsx
+++ b/public/templates/office/EMP_DEG_070_코드정의서.xlsx
@@ -2898,7 +2898,7 @@
       </c>
       <c r="C12" s="236" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="265" t="n"/>
@@ -2956,7 +2956,7 @@
     <row r="22" ht="24" customHeight="1" s="264">
       <c r="C22" s="268" t="inlineStr">
         <is>
-          <t>그로브소프트 (EMPASY)</t>
+          <t>엠파시 (EMPASY)</t>
         </is>
       </c>
       <c r="D22" s="269" t="n"/>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="C4" s="280" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 사원번호 (예: AP100456)</t>
+          <t>한빛글로벌 사원번호 (예: AP100456)</t>
         </is>
       </c>
       <c r="D4" s="280" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C5" s="280" t="inlineStr">
         <is>
-          <t>사용자 실명 (예: 김경호)</t>
+          <t>사용자 실명 (예: 한승우)</t>
         </is>
       </c>
       <c r="D5" s="280" t="inlineStr">
@@ -6546,7 +6546,7 @@
       <c r="J11" s="285" t="inlineStr"/>
       <c r="K11" s="288" t="inlineStr">
         <is>
-          <t>화장품법 제13조 표시광고 위반 및 의약품 오인 우려</t>
+          <t>표시·광고 공정화법 제3조 표시광고 위반 및 의약품 오인 우려</t>
         </is>
       </c>
       <c r="L11" s="182" t="n"/>
@@ -7806,7 +7806,7 @@
       <c r="J31" s="291" t="n"/>
       <c r="K31" s="290" t="inlineStr">
         <is>
-          <t>server-api (:18085) 대외 인터페이스(티움넷/마이비커) 및 300MB 파일 API 서버</t>
+          <t>server-api (:18085) 대외 인터페이스(마케팅허브/프로덕트랩) 및 300MB 파일 API 서버</t>
         </is>
       </c>
       <c r="L31" s="185" t="n"/>
@@ -8184,7 +8184,7 @@
       <c r="J37" s="291" t="inlineStr"/>
       <c r="K37" s="290" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 전문</t>
+          <t>식약처 제품 표시·광고 가이드라인 전문</t>
         </is>
       </c>
       <c r="L37" s="185" t="n"/>
@@ -8373,7 +8373,7 @@
       <c r="J40" s="294" t="inlineStr"/>
       <c r="K40" s="294" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 브랜드별 자율 심의 가이드</t>
+          <t>한빛글로벌 브랜드별 자율 심의 가이드</t>
         </is>
       </c>
     </row>

--- a/public/templates/office/EMP_DEG_070_코드정의서.xlsx
+++ b/public/templates/office/EMP_DEG_070_코드정의서.xlsx
@@ -2898,7 +2898,7 @@
       </c>
       <c r="C12" s="236" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="265" t="n"/>
@@ -2962,7 +2962,7 @@
       <c r="D22" s="269" t="n"/>
       <c r="E22" s="270" t="inlineStr">
         <is>
-          <t>고객사명</t>
+          <t>주식회사 한빛글로벌</t>
         </is>
       </c>
       <c r="F22" s="271" t="n"/>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="D4" s="278" t="inlineStr">
         <is>
-          <t>SyncGuard AI 시스템 구축 기준 상세 작성</t>
+          <t>SyncFlow AI 시스템 구축 기준 상세 작성</t>
         </is>
       </c>
       <c r="E4" s="278" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D5" s="138" t="inlineStr">
         <is>
-          <t>심의상태(QUEUED 대기열, FAILED 분석실패), OCR 엔진 선택 코드(OCR_PROVIDER: NAVER/PADDLE/AUTO), 5대 모듈 서버 역할 코드(SERVER_ROLE) 반영</t>
+          <t>검증상태(QUEUED 대기열, FAILED 분석실패), OCR 엔진 선택 코드(OCR_PROVIDER: NAVER/PADDLE/AUTO), 5대 모듈 서버 역할 코드(SERVER_ROLE) 반영</t>
         </is>
       </c>
       <c r="E5" s="139" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="C4" s="280" t="inlineStr">
         <is>
-          <t>한빛글로벌 사원번호 (예: AP100456)</t>
+          <t>한빛글로벌 사원번호 (예: HB100456)</t>
         </is>
       </c>
       <c r="D4" s="280" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="C8" s="280" t="inlineStr">
         <is>
-          <t>ROLE_MARKETER / ROLE_RA / ROLE_ADMIN</t>
+          <t>ROLE_MARKETER / ROLE_QA / ROLE_ADMIN</t>
         </is>
       </c>
       <c r="D8" s="280" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D9" s="280" t="inlineStr">
         <is>
-          <t>심의 완료 및 긴급 알림 발송용</t>
+          <t>검증 완료 및 긴급 알림 발송용</t>
         </is>
       </c>
       <c r="E9" s="92" t="n"/>
@@ -6127,12 +6127,12 @@
       </c>
       <c r="B5" s="282" t="inlineStr">
         <is>
-          <t>REVIEW_STATUS</t>
+          <t>VERIFY_STATUS</t>
         </is>
       </c>
       <c r="C5" s="283" t="inlineStr">
         <is>
-          <t>심의상태</t>
+          <t>검증상태</t>
         </is>
       </c>
       <c r="D5" s="284" t="inlineStr">
@@ -6168,7 +6168,7 @@
       <c r="J5" s="283" t="inlineStr"/>
       <c r="K5" s="287" t="inlineStr">
         <is>
-          <t>마케터 시안 업로드 후 기본 정보 입력 중</t>
+          <t>구매담당자 계약·도서 업로드 후 기본 정보 입력 중</t>
         </is>
       </c>
       <c r="L5" s="173" t="n"/>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="B6" s="282" t="inlineStr">
         <is>
-          <t>REVIEW_STATUS</t>
+          <t>VERIFY_STATUS</t>
         </is>
       </c>
       <c r="C6" s="283" t="inlineStr">
         <is>
-          <t>심의상태</t>
+          <t>검증상태</t>
         </is>
       </c>
       <c r="D6" s="286" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="E6" s="283" t="inlineStr">
         <is>
-          <t>심의요청</t>
+          <t>검증요청</t>
         </is>
       </c>
       <c r="F6" s="286" t="inlineStr">
@@ -6231,7 +6231,7 @@
       <c r="J6" s="283" t="inlineStr"/>
       <c r="K6" s="287" t="inlineStr">
         <is>
-          <t>심의 접수 완료 및 AI 판정 대기</t>
+          <t>검증 접수 완료 및 AI 판정 대기</t>
         </is>
       </c>
       <c r="L6" s="178" t="n"/>
@@ -6253,12 +6253,12 @@
       </c>
       <c r="B7" s="282" t="inlineStr">
         <is>
-          <t>REVIEW_STATUS</t>
+          <t>VERIFY_STATUS</t>
         </is>
       </c>
       <c r="C7" s="283" t="inlineStr">
         <is>
-          <t>심의상태</t>
+          <t>검증상태</t>
         </is>
       </c>
       <c r="D7" s="286" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="B8" s="282" t="inlineStr">
         <is>
-          <t>REVIEW_STATUS</t>
+          <t>VERIFY_STATUS</t>
         </is>
       </c>
       <c r="C8" s="283" t="inlineStr">
         <is>
-          <t>심의상태</t>
+          <t>검증상태</t>
         </is>
       </c>
       <c r="D8" s="286" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E8" s="283" t="inlineStr">
         <is>
-          <t>심의중</t>
+          <t>검증중</t>
         </is>
       </c>
       <c r="F8" s="286" t="inlineStr">
@@ -6357,7 +6357,7 @@
       <c r="J8" s="283" t="inlineStr"/>
       <c r="K8" s="287" t="inlineStr">
         <is>
-          <t>RA 전문가 2D Canvas 시안 대조 및 검토 중</t>
+          <t>법무·QA 전문위원 2D Canvas 계약·도서 대조 및 검토 중</t>
         </is>
       </c>
       <c r="L8" s="178" t="n"/>
@@ -6379,12 +6379,12 @@
       </c>
       <c r="B9" s="282" t="inlineStr">
         <is>
-          <t>REVIEW_STATUS</t>
+          <t>VERIFY_STATUS</t>
         </is>
       </c>
       <c r="C9" s="283" t="inlineStr">
         <is>
-          <t>심의상태</t>
+          <t>검증상태</t>
         </is>
       </c>
       <c r="D9" s="286" t="inlineStr">
@@ -6420,7 +6420,7 @@
       <c r="J9" s="283" t="inlineStr"/>
       <c r="K9" s="287" t="inlineStr">
         <is>
-          <t>시안 보완 필요로 마케터에게 수정 요청</t>
+          <t>계약·도서 보완 필요로 구매담당자에게 수정 요청</t>
         </is>
       </c>
       <c r="L9" s="178" t="n"/>
@@ -6442,12 +6442,12 @@
       </c>
       <c r="B10" s="282" t="inlineStr">
         <is>
-          <t>REVIEW_STATUS</t>
+          <t>VERIFY_STATUS</t>
         </is>
       </c>
       <c r="C10" s="283" t="inlineStr">
         <is>
-          <t>심의상태</t>
+          <t>검증상태</t>
         </is>
       </c>
       <c r="D10" s="286" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="E10" s="283" t="inlineStr">
         <is>
-          <t>심의확정</t>
+          <t>검증확정</t>
         </is>
       </c>
       <c r="F10" s="286" t="inlineStr">
@@ -6483,7 +6483,7 @@
       <c r="J10" s="283" t="inlineStr"/>
       <c r="K10" s="287" t="inlineStr">
         <is>
-          <t>RA 최종 심의 확정 완료 (결과서 발급 및 연계 회신)</t>
+          <t>QA 최종 검증 확정 완료 (결과서 발급 및 연계 회신)</t>
         </is>
       </c>
       <c r="L10" s="178" t="n"/>
@@ -6546,7 +6546,7 @@
       <c r="J11" s="285" t="inlineStr"/>
       <c r="K11" s="288" t="inlineStr">
         <is>
-          <t>표시·광고 공정화법 제3조 표시광고 위반 및 의약품 오인 우려</t>
+          <t>하도급법 제3조의4 계약·기술규격 위반 및 불공정 독소조항 우려</t>
         </is>
       </c>
       <c r="L11" s="182" t="n"/>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="E12" s="283" t="inlineStr">
         <is>
-          <t>주의(실증필요)</t>
+          <t>주의(성적서필요)</t>
         </is>
       </c>
       <c r="F12" s="286" t="inlineStr">
@@ -6609,7 +6609,7 @@
       <c r="J12" s="285" t="inlineStr"/>
       <c r="K12" s="288" t="inlineStr">
         <is>
-          <t>실증자료 제출 필요 또는 문구 수정 권고</t>
+          <t>시험성적서 제출 필요 또는 조항 수정 권고</t>
         </is>
       </c>
       <c r="L12" s="182" t="n"/>
@@ -6672,7 +6672,7 @@
       <c r="J13" s="285" t="inlineStr"/>
       <c r="K13" s="288" t="inlineStr">
         <is>
-          <t>표시광고 법령 및 사내 가이드라인 적합</t>
+          <t>계약·기술규격 법령 및 사내 가이드라인 적합</t>
         </is>
       </c>
       <c r="L13" s="182" t="n"/>
@@ -6798,7 +6798,7 @@
       <c r="J15" s="283" t="inlineStr"/>
       <c r="K15" s="287" t="inlineStr">
         <is>
-          <t>식약처 가이드라인 및 과거 심의사례 근거 검색</t>
+          <t>공정위·표준원 가이드라인 및 과거 검증사례 근거 검색</t>
         </is>
       </c>
       <c r="L15" s="178" t="n"/>
@@ -6861,7 +6861,7 @@
       <c r="J16" s="291" t="inlineStr"/>
       <c r="K16" s="290" t="inlineStr">
         <is>
-          <t>수식어 및 문맥 종합 심의 판정</t>
+          <t>수식어 및 문맥 종합 검증 판정</t>
         </is>
       </c>
       <c r="L16" s="185" t="n"/>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="C17" s="283" t="inlineStr">
         <is>
-          <t>실증상태</t>
+          <t>시험검증상태</t>
         </is>
       </c>
       <c r="D17" s="289" t="inlineStr">
@@ -6924,7 +6924,7 @@
       <c r="J17" s="291" t="inlineStr"/>
       <c r="K17" s="290" t="inlineStr">
         <is>
-          <t>일반 화장품 효능으로 실증 불필요</t>
+          <t>일반 전장부품 성능규격으로 시험검증 불필요</t>
         </is>
       </c>
       <c r="L17" s="185" t="n"/>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="C18" s="283" t="inlineStr">
         <is>
-          <t>실증상태</t>
+          <t>시험검증상태</t>
         </is>
       </c>
       <c r="D18" s="289" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E18" s="290" t="inlineStr">
         <is>
-          <t>실증필요</t>
+          <t>성적서필요</t>
         </is>
       </c>
       <c r="F18" s="286" t="inlineStr">
@@ -6987,7 +6987,7 @@
       <c r="J18" s="291" t="inlineStr"/>
       <c r="K18" s="290" t="inlineStr">
         <is>
-          <t>수치/지속시간/기능성 효능으로 시험성적서 필수</t>
+          <t>수치/지속시간/핵심규격 성능규격으로 시험성적서 필수</t>
         </is>
       </c>
       <c r="L18" s="185" t="n"/>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="C19" s="291" t="inlineStr">
         <is>
-          <t>실증상태</t>
+          <t>시험검증상태</t>
         </is>
       </c>
       <c r="D19" s="289" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="E19" s="290" t="inlineStr">
         <is>
-          <t>실증완료</t>
+          <t>성적서완료</t>
         </is>
       </c>
       <c r="F19" s="286" t="inlineStr">
@@ -7050,7 +7050,7 @@
       <c r="J19" s="291" t="inlineStr"/>
       <c r="K19" s="290" t="inlineStr">
         <is>
-          <t>ProductLab 임상 시험자료 매핑 완료</t>
+          <t>PLM-Nexus 신뢰성 시험자료 매핑 완료</t>
         </is>
       </c>
       <c r="L19" s="185" t="n"/>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="C20" s="291" t="inlineStr">
         <is>
-          <t>실증상태</t>
+          <t>시험검증상태</t>
         </is>
       </c>
       <c r="D20" s="286" t="inlineStr">
@@ -7113,7 +7113,7 @@
       <c r="J20" s="283" t="inlineStr"/>
       <c r="K20" s="287" t="inlineStr">
         <is>
-          <t>실증자료 유효기간 경과</t>
+          <t>시험성적서 유효기간 경과</t>
         </is>
       </c>
       <c r="L20" s="178" t="n"/>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="C21" s="291" t="inlineStr">
         <is>
-          <t>시안파일형식</t>
+          <t>계약·도서파일형식</t>
         </is>
       </c>
       <c r="D21" s="286" t="inlineStr">
@@ -7176,7 +7176,7 @@
       <c r="J21" s="283" t="inlineStr"/>
       <c r="K21" s="287" t="inlineStr">
         <is>
-          <t>마케팅 시안 PPTX (슬라이드별 텍스트/이미지 파싱)</t>
+          <t>구매조달 계약·도서 PPTX (슬라이드별 텍스트/이미지 파싱)</t>
         </is>
       </c>
       <c r="L21" s="178" t="n"/>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="C22" s="291" t="inlineStr">
         <is>
-          <t>시안파일형식</t>
+          <t>계약·도서파일형식</t>
         </is>
       </c>
       <c r="D22" s="286" t="inlineStr">
@@ -7239,7 +7239,7 @@
       <c r="J22" s="283" t="inlineStr"/>
       <c r="K22" s="287" t="inlineStr">
         <is>
-          <t>브로슈어 및 인쇄 시안 PDF</t>
+          <t>브로슈어 및 인쇄 계약·도서 PDF</t>
         </is>
       </c>
       <c r="L22" s="178" t="n"/>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="C23" s="291" t="inlineStr">
         <is>
-          <t>시안파일형식</t>
+          <t>계약·도서파일형식</t>
         </is>
       </c>
       <c r="D23" s="289" t="inlineStr">
@@ -7302,7 +7302,7 @@
       <c r="J23" s="291" t="inlineStr"/>
       <c r="K23" s="290" t="inlineStr">
         <is>
-          <t>온라인 상세페이지/SNS 이미지</t>
+          <t>온라인 계약서/기술시방서 이미지</t>
         </is>
       </c>
       <c r="L23" s="185" t="n"/>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="C24" s="291" t="inlineStr">
         <is>
-          <t>시안파일형식</t>
+          <t>계약·도서파일형식</t>
         </is>
       </c>
       <c r="D24" s="289" t="inlineStr">
@@ -7365,7 +7365,7 @@
       <c r="J24" s="291" t="inlineStr"/>
       <c r="K24" s="290" t="inlineStr">
         <is>
-          <t>온라인 배너 및 패키지 라벨 이미지</t>
+          <t>온라인 배너 및 도면도면도면패키지 라벨 이미지</t>
         </is>
       </c>
       <c r="L24" s="185" t="n"/>
@@ -7387,12 +7387,12 @@
       </c>
       <c r="B25" s="292" t="inlineStr">
         <is>
-          <t>REVIEW_STATUS</t>
+          <t>VERIFY_STATUS</t>
         </is>
       </c>
       <c r="C25" s="291" t="inlineStr">
         <is>
-          <t>심의상태</t>
+          <t>검증상태</t>
         </is>
       </c>
       <c r="D25" s="289" t="inlineStr">
@@ -7450,12 +7450,12 @@
       </c>
       <c r="B26" s="292" t="inlineStr">
         <is>
-          <t>REVIEW_STATUS</t>
+          <t>VERIFY_STATUS</t>
         </is>
       </c>
       <c r="C26" s="291" t="inlineStr">
         <is>
-          <t>심의상태</t>
+          <t>검증상태</t>
         </is>
       </c>
       <c r="D26" s="289" t="inlineStr">
@@ -7518,17 +7518,17 @@
       </c>
       <c r="C27" s="291" t="inlineStr">
         <is>
-          <t>시안파일형식</t>
+          <t>계약·도서파일형식</t>
         </is>
       </c>
       <c r="D27" s="289" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>CAD/PDF</t>
         </is>
       </c>
       <c r="E27" s="290" t="inlineStr">
         <is>
-          <t>MP4 동영상</t>
+          <t>CAD/PDF 설계도면</t>
         </is>
       </c>
       <c r="F27" s="286" t="inlineStr">
@@ -7554,7 +7554,7 @@
       <c r="J27" s="291" t="n"/>
       <c r="K27" s="290" t="inlineStr">
         <is>
-          <t>최대 300MB 동영상 시안 (FO API 직접 업로드 및 장면 캡처)</t>
+          <t>최대 300MB 설계도면 계약·도서 (FO API 직접 업로드 및 장면 스냅샷)</t>
         </is>
       </c>
       <c r="L27" s="185" t="n"/>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="E28" s="290" t="inlineStr">
         <is>
-          <t>네이버 클로바 OCR</t>
+          <t>엔터프라이즈 비전 OCR</t>
         </is>
       </c>
       <c r="F28" s="286" t="inlineStr">
@@ -7617,7 +7617,7 @@
       <c r="J28" s="291" t="n"/>
       <c r="K28" s="290" t="inlineStr">
         <is>
-          <t>Naver Clova OCR API 엔진 사용</t>
+          <t>Enterprise Vision OCR API 엔진 사용</t>
         </is>
       </c>
       <c r="L28" s="185" t="n"/>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="E29" s="290" t="inlineStr">
         <is>
-          <t>패들 OCR</t>
+          <t>도면 OCR</t>
         </is>
       </c>
       <c r="F29" s="286" t="inlineStr">
@@ -7806,7 +7806,7 @@
       <c r="J31" s="291" t="n"/>
       <c r="K31" s="290" t="inlineStr">
         <is>
-          <t>server-api (:18085) 대외 인터페이스(마케팅허브/프로덕트랩) 및 300MB 파일 API 서버</t>
+          <t>server-api (:18085) 대외 인터페이스(전자구매포털/피엘엠넥서스) 및 300MB 파일 API 서버</t>
         </is>
       </c>
       <c r="L31" s="185" t="n"/>
@@ -7869,7 +7869,7 @@
       <c r="J32" s="291" t="n"/>
       <c r="K32" s="290" t="inlineStr">
         <is>
-          <t>server-be (:18080) 통합 심의 워크스페이스 및 RA 백오피스 관리 메인 서버</t>
+          <t>server-be (:18080) 통합 검증 워크스페이스 및 QA 백오피스 관리 메인 서버</t>
         </is>
       </c>
       <c r="L32" s="185" t="n"/>
@@ -7932,7 +7932,7 @@
       <c r="J33" s="291" t="n"/>
       <c r="K33" s="290" t="inlineStr">
         <is>
-          <t>server-ai-agent (:18083) 영상 피크프레임 추출·OCR·RAG·3단계 LLM 워커</t>
+          <t>server-ai-agent (:18083) 영상 도면 규격영역 추출·OCR·RAG·3단계 LLM 워커</t>
         </is>
       </c>
       <c r="L33" s="185" t="n"/>
@@ -7995,7 +7995,7 @@
       <c r="J34" s="291" t="n"/>
       <c r="K34" s="290" t="inlineStr">
         <is>
-          <t>server-batch (:18084) 02:00 ProductLab·02:30 KT레몬 일배치 스케줄러</t>
+          <t>server-batch (:18084) 02:00 PLM-Nexus·02:30 HB-Monitor 일배치 스케줄러</t>
         </is>
       </c>
       <c r="L34" s="185" t="n"/>
@@ -8032,7 +8032,7 @@
       </c>
       <c r="E35" s="290" t="inlineStr">
         <is>
-          <t>권장대체어</t>
+          <t>권장표준대안</t>
         </is>
       </c>
       <c r="F35" s="284" t="inlineStr">
@@ -8058,7 +8058,7 @@
       <c r="J35" s="291" t="inlineStr"/>
       <c r="K35" s="290" t="inlineStr">
         <is>
-          <t>금지/주의 표현 대응 사내 승인 대체 문구</t>
+          <t>금지/주의 표현 대응 사내 승인 대체 조항</t>
         </is>
       </c>
       <c r="L35" s="185" t="n"/>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="E36" s="290" t="inlineStr">
         <is>
-          <t>안전문구</t>
+          <t>안전조항</t>
         </is>
       </c>
       <c r="F36" s="284" t="inlineStr">
@@ -8121,7 +8121,7 @@
       <c r="J36" s="291" t="inlineStr"/>
       <c r="K36" s="290" t="inlineStr">
         <is>
-          <t>표시광고 법령상 자유롭게 사용 가능한 문구</t>
+          <t>계약·기술규격 법령상 자유롭게 사용 가능한 조항</t>
         </is>
       </c>
       <c r="L36" s="185" t="n"/>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="E37" s="290" t="inlineStr">
         <is>
-          <t>식약처 가이드라인</t>
+          <t>공정위·표준원 가이드라인</t>
         </is>
       </c>
       <c r="F37" s="284" t="inlineStr">
@@ -8184,7 +8184,7 @@
       <c r="J37" s="291" t="inlineStr"/>
       <c r="K37" s="290" t="inlineStr">
         <is>
-          <t>식약처 제품 표시·광고 가이드라인 전문</t>
+          <t>공정위·표준원 구매계약·기술규격 가이드라인 전문</t>
         </is>
       </c>
       <c r="L37" s="185" t="n"/>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="E38" s="283" t="inlineStr">
         <is>
-          <t>행정처분 사례집</t>
+          <t>불공정 하도급 심결례집</t>
         </is>
       </c>
       <c r="F38" s="286" t="inlineStr">
@@ -8247,7 +8247,7 @@
       <c r="J38" s="283" t="inlineStr"/>
       <c r="K38" s="287" t="inlineStr">
         <is>
-          <t>식약처 및 지방청 행정처분/시정명령 판례</t>
+          <t>공정위·표준원 및 지방청 시정명령·심결/시정명령 판례</t>
         </is>
       </c>
       <c r="L38" s="178" t="n"/>
@@ -8373,7 +8373,7 @@
       <c r="J40" s="294" t="inlineStr"/>
       <c r="K40" s="294" t="inlineStr">
         <is>
-          <t>한빛글로벌 브랜드별 자율 심의 가이드</t>
+          <t>한빛글로벌 사업부별 자율 검증 가이드</t>
         </is>
       </c>
     </row>
@@ -8395,12 +8395,12 @@
       </c>
       <c r="D41" s="293" t="inlineStr">
         <is>
-          <t>REVIEW_CREATE</t>
+          <t>VERIFY_CREATE</t>
         </is>
       </c>
       <c r="E41" s="294" t="inlineStr">
         <is>
-          <t>심의요청 등록</t>
+          <t>검증요청 등록</t>
         </is>
       </c>
       <c r="F41" s="293" t="inlineStr">
@@ -8426,7 +8426,7 @@
       <c r="J41" s="294" t="inlineStr"/>
       <c r="K41" s="294" t="inlineStr">
         <is>
-          <t>시안 파일 업로드 및 심의 등록</t>
+          <t>계약·도서 파일 업로드 및 검증 등록</t>
         </is>
       </c>
     </row>
@@ -8501,12 +8501,12 @@
       </c>
       <c r="D43" s="293" t="inlineStr">
         <is>
-          <t>RA_EDIT</t>
+          <t>QA_EDIT</t>
         </is>
       </c>
       <c r="E43" s="294" t="inlineStr">
         <is>
-          <t>문안 수정/대체</t>
+          <t>계약조항 수정/대체</t>
         </is>
       </c>
       <c r="F43" s="293" t="inlineStr">
@@ -8532,7 +8532,7 @@
       <c r="J43" s="294" t="inlineStr"/>
       <c r="K43" s="294" t="inlineStr">
         <is>
-          <t>RA 전문가 문안 교정 및 대체어 적용</t>
+          <t>법무·QA 전문위원 계약조항 교정 및 표준대안 적용</t>
         </is>
       </c>
     </row>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="D44" s="293" t="inlineStr">
         <is>
-          <t>RA_CONFIRM</t>
+          <t>QA_CONFIRM</t>
         </is>
       </c>
       <c r="E44" s="294" t="inlineStr">
         <is>
-          <t>심의 최종 확정</t>
+          <t>검증 최종 확정</t>
         </is>
       </c>
       <c r="F44" s="293" t="inlineStr">
@@ -8585,7 +8585,7 @@
       <c r="J44" s="294" t="inlineStr"/>
       <c r="K44" s="294" t="inlineStr">
         <is>
-          <t>RA 최종 심의 승인 및 불변 스냅샷 보존</t>
+          <t>QA 최종 검증 승인 및 불변 스냅샷 보존</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8638,7 @@
       <c r="J45" s="294" t="inlineStr"/>
       <c r="K45" s="294" t="inlineStr">
         <is>
-          <t>식약처 소명용 감사 증적 패키지 다운로드</t>
+          <t>공정위·표준원 소명용 감사 증적 도면도면도면패키지 다운로드</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
     <row r="4" ht="27" customHeight="1" s="264">
       <c r="A4" s="295" t="inlineStr">
         <is>
-          <t>심의신청번호</t>
+          <t>검증신청번호</t>
         </is>
       </c>
       <c r="B4" s="296" t="inlineStr">
@@ -8752,22 +8752,22 @@
       </c>
       <c r="C4" s="295" t="inlineStr">
         <is>
-          <t>CLM</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="D4" s="297" t="inlineStr">
         <is>
-          <t>CLM + YYYYMMDD + 4자리 순번 (예: CLM202610160001)</t>
+          <t>REV + YYYYMMDD + 4자리 순번 (예: REV202610160001)</t>
         </is>
       </c>
       <c r="E4" s="296" t="inlineStr">
         <is>
-          <t>seq_review_no</t>
+          <t>seq_verify_no</t>
         </is>
       </c>
       <c r="F4" s="295" t="inlineStr">
         <is>
-          <t>review_request.review_no</t>
+          <t>verify_request.verify_no</t>
         </is>
       </c>
       <c r="G4" s="295" t="inlineStr">
@@ -8791,7 +8791,7 @@
     <row r="5" ht="27" customHeight="1" s="264">
       <c r="A5" s="295" t="inlineStr">
         <is>
-          <t>실증자료번호</t>
+          <t>시험성적서번호</t>
         </is>
       </c>
       <c r="B5" s="296" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="I5" s="298" t="inlineStr">
         <is>
-          <t>ProductLab 연동 시 채번</t>
+          <t>PLM-Nexus 연동 시 채번</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="F6" s="295" t="inlineStr">
         <is>
-          <t>review_rule_dictionary.rule_no</t>
+          <t>verify_rule_dictionary.rule_no</t>
         </is>
       </c>
       <c r="G6" s="295" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F7" s="295" t="inlineStr">
         <is>
-          <t>review_history_immutable.audit_no</t>
+          <t>verify_history_immutable.audit_no</t>
         </is>
       </c>
       <c r="G7" s="295" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="I7" s="298" t="inlineStr">
         <is>
-          <t>식약처 사후 소명용 불변 키</t>
+          <t>공정위·표준원 사후 소명용 불변 키</t>
         </is>
       </c>
     </row>
